--- a/rcads/data/xls/05_EntityGroupMap.xlsx
+++ b/rcads/data/xls/05_EntityGroupMap.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_05_EntityGroupMap"/>
   </sheets>
   <definedNames>
-    <definedName name="_05_EntityGroupMap">'_05_EntityGroupMap'!$A$1:$C$193</definedName>
+    <definedName name="_05_EntityGroupMap">'_05_EntityGroupMap'!$A$1:$C$217</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C193"/>
+  <dimension ref="A1:C217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -2475,6 +2475,270 @@
         <v>3</v>
       </c>
     </row>
+    <row outlineLevel="0" r="194">
+      <c r="A194" s="0">
+        <v>203</v>
+      </c>
+      <c r="B194" s="0">
+        <v>166</v>
+      </c>
+      <c r="C194" s="0">
+        <v>170</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="195">
+      <c r="A195" s="0">
+        <v>204</v>
+      </c>
+      <c r="B195" s="0">
+        <v>167</v>
+      </c>
+      <c r="C195" s="0">
+        <v>154</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="196">
+      <c r="A196" s="0">
+        <v>205</v>
+      </c>
+      <c r="B196" s="0">
+        <v>167</v>
+      </c>
+      <c r="C196" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="197">
+      <c r="A197" s="0">
+        <v>206</v>
+      </c>
+      <c r="B197" s="0">
+        <v>168</v>
+      </c>
+      <c r="C197" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="198">
+      <c r="A198" s="0">
+        <v>207</v>
+      </c>
+      <c r="B198" s="0">
+        <v>169</v>
+      </c>
+      <c r="C198" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="199">
+      <c r="A199" s="0">
+        <v>208</v>
+      </c>
+      <c r="B199" s="0">
+        <v>169</v>
+      </c>
+      <c r="C199" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="200">
+      <c r="A200" s="0">
+        <v>209</v>
+      </c>
+      <c r="B200" s="0">
+        <v>170</v>
+      </c>
+      <c r="C200" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="201">
+      <c r="A201" s="0">
+        <v>210</v>
+      </c>
+      <c r="B201" s="0">
+        <v>172</v>
+      </c>
+      <c r="C201" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="202">
+      <c r="A202" s="0">
+        <v>211</v>
+      </c>
+      <c r="B202" s="0">
+        <v>173</v>
+      </c>
+      <c r="C202" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="203">
+      <c r="A203" s="0">
+        <v>212</v>
+      </c>
+      <c r="B203" s="0">
+        <v>171</v>
+      </c>
+      <c r="C203" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="204">
+      <c r="A204" s="0">
+        <v>213</v>
+      </c>
+      <c r="B204" s="0">
+        <v>174</v>
+      </c>
+      <c r="C204" s="0">
+        <v>162</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="205">
+      <c r="A205" s="0">
+        <v>214</v>
+      </c>
+      <c r="B205" s="0">
+        <v>175</v>
+      </c>
+      <c r="C205" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="206">
+      <c r="A206" s="0">
+        <v>215</v>
+      </c>
+      <c r="B206" s="0">
+        <v>176</v>
+      </c>
+      <c r="C206" s="0">
+        <v>174</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="207">
+      <c r="A207" s="0">
+        <v>216</v>
+      </c>
+      <c r="B207" s="0">
+        <v>177</v>
+      </c>
+      <c r="C207" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="208">
+      <c r="A208" s="0">
+        <v>217</v>
+      </c>
+      <c r="B208" s="0">
+        <v>178</v>
+      </c>
+      <c r="C208" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="209">
+      <c r="A209" s="0">
+        <v>218</v>
+      </c>
+      <c r="B209" s="0">
+        <v>179</v>
+      </c>
+      <c r="C209" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="210">
+      <c r="A210" s="0">
+        <v>219</v>
+      </c>
+      <c r="B210" s="0">
+        <v>178</v>
+      </c>
+      <c r="C210" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="211">
+      <c r="A211" s="0">
+        <v>220</v>
+      </c>
+      <c r="B211" s="0">
+        <v>179</v>
+      </c>
+      <c r="C211" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="212">
+      <c r="A212" s="0">
+        <v>221</v>
+      </c>
+      <c r="B212" s="0">
+        <v>180</v>
+      </c>
+      <c r="C212" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="213">
+      <c r="A213" s="0">
+        <v>222</v>
+      </c>
+      <c r="B213" s="0">
+        <v>182</v>
+      </c>
+      <c r="C213" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="214">
+      <c r="A214" s="0">
+        <v>223</v>
+      </c>
+      <c r="B214" s="0">
+        <v>182</v>
+      </c>
+      <c r="C214" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="215">
+      <c r="A215" s="0">
+        <v>224</v>
+      </c>
+      <c r="B215" s="0">
+        <v>181</v>
+      </c>
+      <c r="C215" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="216">
+      <c r="A216" s="0">
+        <v>225</v>
+      </c>
+      <c r="B216" s="0">
+        <v>183</v>
+      </c>
+      <c r="C216" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="217">
+      <c r="A217" s="0">
+        <v>226</v>
+      </c>
+      <c r="B217" s="0">
+        <v>179</v>
+      </c>
+      <c r="C217" s="0">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
